--- a/FinanceDataMigration/src/main/resources/migration-templates/JOURNAL_VOUCHER.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/JOURNAL_VOUCHER.xlsx
@@ -1281,7 +1281,7 @@
       </c>
       <c r="O5" s="25"/>
       <c r="P5" s="23">
-        <v>1100100004</v>
+        <v>1100100001</v>
       </c>
       <c r="Q5" s="27">
         <v>1230</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O7" s="25"/>
       <c r="P7" s="23">
-        <v>1100100002</v>
+        <v>110010000</v>
       </c>
       <c r="Q7" s="27">
         <v>4321</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="O20" s="31"/>
       <c r="P20" s="25">
-        <v>1100100011</v>
+        <v>1100100002</v>
       </c>
       <c r="Q20" s="31">
         <v>7863</v>
@@ -2303,9 +2303,7 @@
       <c r="Z29" s="17"/>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="22">
-        <v>26</v>
-      </c>
+      <c r="A30" s="22"/>
       <c r="B30" s="31"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
@@ -2333,9 +2331,7 @@
       <c r="Z30" s="17"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="22">
-        <v>27</v>
-      </c>
+      <c r="A31" s="22"/>
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
@@ -2363,9 +2359,7 @@
       <c r="Z31" s="17"/>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="22">
-        <v>28</v>
-      </c>
+      <c r="A32" s="22"/>
       <c r="B32" s="31"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
@@ -2393,9 +2387,7 @@
       <c r="Z32" s="17"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="22">
-        <v>29</v>
-      </c>
+      <c r="A33" s="22"/>
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
@@ -2423,9 +2415,7 @@
       <c r="Z33" s="17"/>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="22">
-        <v>30</v>
-      </c>
+      <c r="A34" s="22"/>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
@@ -2453,9 +2443,7 @@
       <c r="Z34" s="17"/>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="22">
-        <v>31</v>
-      </c>
+      <c r="A35" s="22"/>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
@@ -2483,9 +2471,7 @@
       <c r="Z35" s="17"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="22">
-        <v>32</v>
-      </c>
+      <c r="A36" s="22"/>
       <c r="B36" s="31"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
@@ -2513,9 +2499,7 @@
       <c r="Z36" s="17"/>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="22">
-        <v>33</v>
-      </c>
+      <c r="A37" s="22"/>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
       <c r="D37" s="31"/>
@@ -2543,9 +2527,7 @@
       <c r="Z37" s="17"/>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="22">
-        <v>34</v>
-      </c>
+      <c r="A38" s="22"/>
       <c r="B38" s="31"/>
       <c r="C38" s="31"/>
       <c r="D38" s="31"/>
@@ -2573,9 +2555,7 @@
       <c r="Z38" s="17"/>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="22">
-        <v>35</v>
-      </c>
+      <c r="A39" s="22"/>
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
       <c r="D39" s="31"/>
@@ -2603,9 +2583,7 @@
       <c r="Z39" s="17"/>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="22">
-        <v>36</v>
-      </c>
+      <c r="A40" s="22"/>
       <c r="B40" s="31"/>
       <c r="C40" s="31"/>
       <c r="D40" s="31"/>
@@ -2633,9 +2611,7 @@
       <c r="Z40" s="17"/>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="22">
-        <v>37</v>
-      </c>
+      <c r="A41" s="22"/>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="31"/>
@@ -2663,9 +2639,7 @@
       <c r="Z41" s="17"/>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="22">
-        <v>38</v>
-      </c>
+      <c r="A42" s="22"/>
       <c r="B42" s="31"/>
       <c r="C42" s="31"/>
       <c r="D42" s="31"/>
@@ -2693,9 +2667,7 @@
       <c r="Z42" s="17"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="22">
-        <v>39</v>
-      </c>
+      <c r="A43" s="22"/>
       <c r="B43" s="31"/>
       <c r="C43" s="31"/>
       <c r="D43" s="31"/>
@@ -2723,9 +2695,7 @@
       <c r="Z43" s="17"/>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="22">
-        <v>40</v>
-      </c>
+      <c r="A44" s="22"/>
       <c r="B44" s="31"/>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
@@ -2753,9 +2723,7 @@
       <c r="Z44" s="17"/>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="22">
-        <v>41</v>
-      </c>
+      <c r="A45" s="22"/>
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
@@ -2783,9 +2751,7 @@
       <c r="Z45" s="17"/>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="22">
-        <v>42</v>
-      </c>
+      <c r="A46" s="22"/>
       <c r="B46" s="31"/>
       <c r="C46" s="31"/>
       <c r="D46" s="31"/>
@@ -2813,9 +2779,7 @@
       <c r="Z46" s="17"/>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="22">
-        <v>43</v>
-      </c>
+      <c r="A47" s="22"/>
       <c r="B47" s="31"/>
       <c r="C47" s="31"/>
       <c r="D47" s="31"/>
@@ -2843,9 +2807,7 @@
       <c r="Z47" s="17"/>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="22">
-        <v>44</v>
-      </c>
+      <c r="A48" s="22"/>
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="31"/>
@@ -2873,9 +2835,7 @@
       <c r="Z48" s="17"/>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="22">
-        <v>45</v>
-      </c>
+      <c r="A49" s="22"/>
       <c r="B49" s="31"/>
       <c r="C49" s="31"/>
       <c r="D49" s="31"/>
@@ -2903,9 +2863,7 @@
       <c r="Z49" s="17"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="22">
-        <v>46</v>
-      </c>
+      <c r="A50" s="22"/>
       <c r="B50" s="31"/>
       <c r="C50" s="31"/>
       <c r="D50" s="31"/>
@@ -2933,9 +2891,7 @@
       <c r="Z50" s="17"/>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="22">
-        <v>47</v>
-      </c>
+      <c r="A51" s="22"/>
       <c r="B51" s="31"/>
       <c r="C51" s="31"/>
       <c r="D51" s="31"/>
@@ -2963,9 +2919,7 @@
       <c r="Z51" s="17"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="22">
-        <v>48</v>
-      </c>
+      <c r="A52" s="22"/>
       <c r="B52" s="31"/>
       <c r="C52" s="31"/>
       <c r="D52" s="31"/>
@@ -2993,9 +2947,7 @@
       <c r="Z52" s="17"/>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="22">
-        <v>49</v>
-      </c>
+      <c r="A53" s="22"/>
       <c r="B53" s="31"/>
       <c r="C53" s="31"/>
       <c r="D53" s="31"/>
@@ -3023,9 +2975,7 @@
       <c r="Z53" s="17"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="22">
-        <v>50</v>
-      </c>
+      <c r="A54" s="22"/>
       <c r="B54" s="31"/>
       <c r="C54" s="31"/>
       <c r="D54" s="31"/>
@@ -3053,9 +3003,7 @@
       <c r="Z54" s="17"/>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="22">
-        <v>51</v>
-      </c>
+      <c r="A55" s="22"/>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
       <c r="D55" s="31"/>
@@ -3083,9 +3031,7 @@
       <c r="Z55" s="17"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="22">
-        <v>52</v>
-      </c>
+      <c r="A56" s="22"/>
       <c r="B56" s="31"/>
       <c r="C56" s="31"/>
       <c r="D56" s="31"/>
@@ -3113,9 +3059,7 @@
       <c r="Z56" s="17"/>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="22">
-        <v>53</v>
-      </c>
+      <c r="A57" s="22"/>
       <c r="B57" s="31"/>
       <c r="C57" s="31"/>
       <c r="D57" s="31"/>
@@ -3143,9 +3087,7 @@
       <c r="Z57" s="17"/>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="22">
-        <v>54</v>
-      </c>
+      <c r="A58" s="22"/>
       <c r="B58" s="31"/>
       <c r="C58" s="31"/>
       <c r="D58" s="31"/>
@@ -3173,9 +3115,7 @@
       <c r="Z58" s="17"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="22">
-        <v>55</v>
-      </c>
+      <c r="A59" s="22"/>
       <c r="B59" s="31"/>
       <c r="C59" s="31"/>
       <c r="D59" s="31"/>
@@ -3203,9 +3143,7 @@
       <c r="Z59" s="17"/>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="22">
-        <v>56</v>
-      </c>
+      <c r="A60" s="22"/>
       <c r="B60" s="31"/>
       <c r="C60" s="31"/>
       <c r="D60" s="31"/>
@@ -3233,9 +3171,7 @@
       <c r="Z60" s="17"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="22">
-        <v>57</v>
-      </c>
+      <c r="A61" s="22"/>
       <c r="B61" s="31"/>
       <c r="C61" s="31"/>
       <c r="D61" s="31"/>
@@ -3263,9 +3199,7 @@
       <c r="Z61" s="17"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="22">
-        <v>58</v>
-      </c>
+      <c r="A62" s="22"/>
       <c r="B62" s="31"/>
       <c r="C62" s="31"/>
       <c r="D62" s="31"/>
@@ -3293,9 +3227,7 @@
       <c r="Z62" s="17"/>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="22">
-        <v>59</v>
-      </c>
+      <c r="A63" s="22"/>
       <c r="B63" s="31"/>
       <c r="C63" s="31"/>
       <c r="D63" s="31"/>
@@ -3323,9 +3255,7 @@
       <c r="Z63" s="17"/>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="22">
-        <v>60</v>
-      </c>
+      <c r="A64" s="22"/>
       <c r="B64" s="31"/>
       <c r="C64" s="31"/>
       <c r="D64" s="31"/>
@@ -3353,9 +3283,7 @@
       <c r="Z64" s="17"/>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="22">
-        <v>61</v>
-      </c>
+      <c r="A65" s="22"/>
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
       <c r="D65" s="31"/>
@@ -3383,9 +3311,7 @@
       <c r="Z65" s="17"/>
     </row>
     <row r="66" ht="14.25">
-      <c r="A66" s="22">
-        <v>62</v>
-      </c>
+      <c r="A66" s="22"/>
       <c r="B66" s="31"/>
       <c r="C66" s="31"/>
       <c r="D66" s="31"/>
@@ -3413,9 +3339,7 @@
       <c r="Z66" s="17"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="22">
-        <v>63</v>
-      </c>
+      <c r="A67" s="22"/>
       <c r="B67" s="31"/>
       <c r="C67" s="31"/>
       <c r="D67" s="31"/>
@@ -3443,9 +3367,7 @@
       <c r="Z67" s="17"/>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="22">
-        <v>64</v>
-      </c>
+      <c r="A68" s="22"/>
       <c r="B68" s="31"/>
       <c r="C68" s="31"/>
       <c r="D68" s="31"/>
@@ -3473,9 +3395,7 @@
       <c r="Z68" s="17"/>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="22">
-        <v>65</v>
-      </c>
+      <c r="A69" s="22"/>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
       <c r="D69" s="31"/>
@@ -3503,9 +3423,7 @@
       <c r="Z69" s="17"/>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="22">
-        <v>66</v>
-      </c>
+      <c r="A70" s="22"/>
       <c r="B70" s="31"/>
       <c r="C70" s="31"/>
       <c r="D70" s="31"/>
@@ -3533,9 +3451,7 @@
       <c r="Z70" s="17"/>
     </row>
     <row r="71" ht="14.25">
-      <c r="A71" s="22">
-        <v>67</v>
-      </c>
+      <c r="A71" s="22"/>
       <c r="B71" s="31"/>
       <c r="C71" s="31"/>
       <c r="D71" s="31"/>
@@ -3563,9 +3479,7 @@
       <c r="Z71" s="17"/>
     </row>
     <row r="72" ht="14.25">
-      <c r="A72" s="22">
-        <v>68</v>
-      </c>
+      <c r="A72" s="22"/>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
       <c r="D72" s="31"/>
@@ -3593,9 +3507,7 @@
       <c r="Z72" s="17"/>
     </row>
     <row r="73" ht="14.25">
-      <c r="A73" s="22">
-        <v>69</v>
-      </c>
+      <c r="A73" s="22"/>
       <c r="B73" s="31"/>
       <c r="C73" s="31"/>
       <c r="D73" s="31"/>
@@ -3623,9 +3535,7 @@
       <c r="Z73" s="17"/>
     </row>
     <row r="74" ht="14.25">
-      <c r="A74" s="22">
-        <v>70</v>
-      </c>
+      <c r="A74" s="22"/>
       <c r="B74" s="31"/>
       <c r="C74" s="31"/>
       <c r="D74" s="31"/>
@@ -3653,9 +3563,7 @@
       <c r="Z74" s="17"/>
     </row>
     <row r="75" ht="14.25">
-      <c r="A75" s="22">
-        <v>71</v>
-      </c>
+      <c r="A75" s="22"/>
       <c r="B75" s="31"/>
       <c r="C75" s="31"/>
       <c r="D75" s="31"/>
@@ -3683,9 +3591,7 @@
       <c r="Z75" s="17"/>
     </row>
     <row r="76" ht="14.25">
-      <c r="A76" s="22">
-        <v>72</v>
-      </c>
+      <c r="A76" s="22"/>
       <c r="B76" s="31"/>
       <c r="C76" s="31"/>
       <c r="D76" s="31"/>
@@ -3713,9 +3619,7 @@
       <c r="Z76" s="17"/>
     </row>
     <row r="77" ht="14.25">
-      <c r="A77" s="22">
-        <v>73</v>
-      </c>
+      <c r="A77" s="22"/>
       <c r="B77" s="31"/>
       <c r="C77" s="31"/>
       <c r="D77" s="31"/>
@@ -3743,9 +3647,7 @@
       <c r="Z77" s="17"/>
     </row>
     <row r="78" ht="14.25">
-      <c r="A78" s="22">
-        <v>74</v>
-      </c>
+      <c r="A78" s="22"/>
       <c r="B78" s="31"/>
       <c r="C78" s="31"/>
       <c r="D78" s="31"/>
@@ -3773,9 +3675,7 @@
       <c r="Z78" s="17"/>
     </row>
     <row r="79" ht="14.25">
-      <c r="A79" s="22">
-        <v>75</v>
-      </c>
+      <c r="A79" s="22"/>
       <c r="B79" s="31"/>
       <c r="C79" s="31"/>
       <c r="D79" s="31"/>
@@ -3803,9 +3703,7 @@
       <c r="Z79" s="17"/>
     </row>
     <row r="80" ht="14.25">
-      <c r="A80" s="22">
-        <v>76</v>
-      </c>
+      <c r="A80" s="22"/>
       <c r="B80" s="31"/>
       <c r="C80" s="31"/>
       <c r="D80" s="31"/>
@@ -3833,9 +3731,7 @@
       <c r="Z80" s="17"/>
     </row>
     <row r="81" ht="14.25">
-      <c r="A81" s="22">
-        <v>77</v>
-      </c>
+      <c r="A81" s="22"/>
       <c r="B81" s="31"/>
       <c r="C81" s="31"/>
       <c r="D81" s="31"/>
@@ -3863,9 +3759,7 @@
       <c r="Z81" s="17"/>
     </row>
     <row r="82" ht="14.25">
-      <c r="A82" s="22">
-        <v>78</v>
-      </c>
+      <c r="A82" s="22"/>
       <c r="B82" s="31"/>
       <c r="C82" s="31"/>
       <c r="D82" s="31"/>
@@ -3893,9 +3787,7 @@
       <c r="Z82" s="17"/>
     </row>
     <row r="83" ht="14.25">
-      <c r="A83" s="22">
-        <v>79</v>
-      </c>
+      <c r="A83" s="22"/>
       <c r="B83" s="31"/>
       <c r="C83" s="31"/>
       <c r="D83" s="31"/>
@@ -3923,9 +3815,7 @@
       <c r="Z83" s="17"/>
     </row>
     <row r="84" ht="14.25">
-      <c r="A84" s="22">
-        <v>80</v>
-      </c>
+      <c r="A84" s="22"/>
       <c r="B84" s="31"/>
       <c r="C84" s="31"/>
       <c r="D84" s="31"/>
@@ -3953,9 +3843,7 @@
       <c r="Z84" s="17"/>
     </row>
     <row r="85" ht="14.25">
-      <c r="A85" s="22">
-        <v>81</v>
-      </c>
+      <c r="A85" s="22"/>
       <c r="B85" s="31"/>
       <c r="C85" s="31"/>
       <c r="D85" s="31"/>
@@ -3983,9 +3871,7 @@
       <c r="Z85" s="17"/>
     </row>
     <row r="86" ht="14.25">
-      <c r="A86" s="22">
-        <v>82</v>
-      </c>
+      <c r="A86" s="22"/>
       <c r="B86" s="31"/>
       <c r="C86" s="31"/>
       <c r="D86" s="31"/>
@@ -4013,9 +3899,7 @@
       <c r="Z86" s="17"/>
     </row>
     <row r="87" ht="14.25">
-      <c r="A87" s="22">
-        <v>83</v>
-      </c>
+      <c r="A87" s="22"/>
       <c r="B87" s="31"/>
       <c r="C87" s="31"/>
       <c r="D87" s="31"/>
@@ -4043,9 +3927,7 @@
       <c r="Z87" s="17"/>
     </row>
     <row r="88" ht="14.25">
-      <c r="A88" s="22">
-        <v>84</v>
-      </c>
+      <c r="A88" s="22"/>
       <c r="B88" s="31"/>
       <c r="C88" s="31"/>
       <c r="D88" s="31"/>
@@ -4073,9 +3955,7 @@
       <c r="Z88" s="17"/>
     </row>
     <row r="89" ht="14.25">
-      <c r="A89" s="22">
-        <v>85</v>
-      </c>
+      <c r="A89" s="22"/>
       <c r="B89" s="31"/>
       <c r="C89" s="31"/>
       <c r="D89" s="31"/>
@@ -4103,9 +3983,7 @@
       <c r="Z89" s="17"/>
     </row>
     <row r="90" ht="14.25">
-      <c r="A90" s="22">
-        <v>86</v>
-      </c>
+      <c r="A90" s="22"/>
       <c r="B90" s="31"/>
       <c r="C90" s="31"/>
       <c r="D90" s="31"/>
@@ -4133,9 +4011,7 @@
       <c r="Z90" s="17"/>
     </row>
     <row r="91" ht="14.25">
-      <c r="A91" s="22">
-        <v>87</v>
-      </c>
+      <c r="A91" s="22"/>
       <c r="B91" s="31"/>
       <c r="C91" s="31"/>
       <c r="D91" s="31"/>
@@ -4163,9 +4039,7 @@
       <c r="Z91" s="17"/>
     </row>
     <row r="92" ht="14.25">
-      <c r="A92" s="22">
-        <v>88</v>
-      </c>
+      <c r="A92" s="22"/>
       <c r="B92" s="31"/>
       <c r="C92" s="31"/>
       <c r="D92" s="31"/>
@@ -4193,9 +4067,7 @@
       <c r="Z92" s="17"/>
     </row>
     <row r="93" ht="14.25">
-      <c r="A93" s="22">
-        <v>89</v>
-      </c>
+      <c r="A93" s="22"/>
       <c r="B93" s="31"/>
       <c r="C93" s="31"/>
       <c r="D93" s="31"/>
@@ -4223,9 +4095,7 @@
       <c r="Z93" s="17"/>
     </row>
     <row r="94" ht="14.25">
-      <c r="A94" s="22">
-        <v>90</v>
-      </c>
+      <c r="A94" s="22"/>
       <c r="B94" s="31"/>
       <c r="C94" s="31"/>
       <c r="D94" s="31"/>
@@ -4253,9 +4123,7 @@
       <c r="Z94" s="17"/>
     </row>
     <row r="95" ht="14.25">
-      <c r="A95" s="22">
-        <v>91</v>
-      </c>
+      <c r="A95" s="22"/>
       <c r="B95" s="31"/>
       <c r="C95" s="31"/>
       <c r="D95" s="31"/>
@@ -4283,9 +4151,7 @@
       <c r="Z95" s="17"/>
     </row>
     <row r="96" ht="14.25">
-      <c r="A96" s="22">
-        <v>92</v>
-      </c>
+      <c r="A96" s="22"/>
       <c r="B96" s="31"/>
       <c r="C96" s="31"/>
       <c r="D96" s="31"/>
@@ -4313,9 +4179,7 @@
       <c r="Z96" s="17"/>
     </row>
     <row r="97" ht="14.25">
-      <c r="A97" s="22">
-        <v>93</v>
-      </c>
+      <c r="A97" s="22"/>
       <c r="B97" s="31"/>
       <c r="C97" s="31"/>
       <c r="D97" s="31"/>
@@ -4343,9 +4207,7 @@
       <c r="Z97" s="17"/>
     </row>
     <row r="98" ht="14.25">
-      <c r="A98" s="22">
-        <v>94</v>
-      </c>
+      <c r="A98" s="22"/>
       <c r="B98" s="31"/>
       <c r="C98" s="31"/>
       <c r="D98" s="31"/>
@@ -4373,9 +4235,7 @@
       <c r="Z98" s="17"/>
     </row>
     <row r="99" ht="14.25">
-      <c r="A99" s="22">
-        <v>95</v>
-      </c>
+      <c r="A99" s="22"/>
       <c r="B99" s="31"/>
       <c r="C99" s="31"/>
       <c r="D99" s="31"/>
@@ -4403,9 +4263,7 @@
       <c r="Z99" s="17"/>
     </row>
     <row r="100" ht="14.25">
-      <c r="A100" s="22">
-        <v>96</v>
-      </c>
+      <c r="A100" s="22"/>
       <c r="B100" s="31"/>
       <c r="C100" s="31"/>
       <c r="D100" s="31"/>
@@ -4433,9 +4291,7 @@
       <c r="Z100" s="17"/>
     </row>
     <row r="101" ht="14.25">
-      <c r="A101" s="22">
-        <v>97</v>
-      </c>
+      <c r="A101" s="22"/>
       <c r="B101" s="31"/>
       <c r="C101" s="31"/>
       <c r="D101" s="31"/>
@@ -4463,9 +4319,7 @@
       <c r="Z101" s="17"/>
     </row>
     <row r="102" ht="14.25">
-      <c r="A102" s="22">
-        <v>98</v>
-      </c>
+      <c r="A102" s="22"/>
       <c r="B102" s="31"/>
       <c r="C102" s="31"/>
       <c r="D102" s="31"/>
@@ -4493,9 +4347,7 @@
       <c r="Z102" s="17"/>
     </row>
     <row r="103" ht="14.25">
-      <c r="A103" s="22">
-        <v>99</v>
-      </c>
+      <c r="A103" s="22"/>
       <c r="B103" s="31"/>
       <c r="C103" s="31"/>
       <c r="D103" s="31"/>
@@ -4523,9 +4375,7 @@
       <c r="Z103" s="17"/>
     </row>
     <row r="104" ht="14.25">
-      <c r="A104" s="22">
-        <v>100</v>
-      </c>
+      <c r="A104" s="22"/>
       <c r="B104" s="31"/>
       <c r="C104" s="31"/>
       <c r="D104" s="31"/>
@@ -4553,9 +4403,7 @@
       <c r="Z104" s="17"/>
     </row>
     <row r="105" ht="14.25">
-      <c r="A105" s="22">
-        <v>101</v>
-      </c>
+      <c r="A105" s="22"/>
       <c r="B105" s="31"/>
       <c r="C105" s="31"/>
       <c r="D105" s="31"/>
@@ -4583,9 +4431,7 @@
       <c r="Z105" s="17"/>
     </row>
     <row r="106" ht="14.25">
-      <c r="A106" s="22">
-        <v>102</v>
-      </c>
+      <c r="A106" s="22"/>
       <c r="B106" s="31"/>
       <c r="C106" s="31"/>
       <c r="D106" s="31"/>
@@ -4613,9 +4459,7 @@
       <c r="Z106" s="17"/>
     </row>
     <row r="107" ht="14.25">
-      <c r="A107" s="22">
-        <v>103</v>
-      </c>
+      <c r="A107" s="22"/>
       <c r="B107" s="31"/>
       <c r="C107" s="31"/>
       <c r="D107" s="31"/>
@@ -4643,9 +4487,7 @@
       <c r="Z107" s="17"/>
     </row>
     <row r="108" ht="14.25">
-      <c r="A108" s="22">
-        <v>104</v>
-      </c>
+      <c r="A108" s="22"/>
       <c r="B108" s="31"/>
       <c r="C108" s="31"/>
       <c r="D108" s="31"/>
@@ -4673,9 +4515,7 @@
       <c r="Z108" s="17"/>
     </row>
     <row r="109" ht="14.25">
-      <c r="A109" s="22">
-        <v>105</v>
-      </c>
+      <c r="A109" s="22"/>
       <c r="B109" s="31"/>
       <c r="C109" s="31"/>
       <c r="D109" s="31"/>
@@ -4703,9 +4543,7 @@
       <c r="Z109" s="17"/>
     </row>
     <row r="110" ht="14.25">
-      <c r="A110" s="22">
-        <v>106</v>
-      </c>
+      <c r="A110" s="22"/>
       <c r="B110" s="31"/>
       <c r="C110" s="31"/>
       <c r="D110" s="31"/>
@@ -4733,9 +4571,7 @@
       <c r="Z110" s="17"/>
     </row>
     <row r="111" ht="14.25">
-      <c r="A111" s="22">
-        <v>107</v>
-      </c>
+      <c r="A111" s="22"/>
       <c r="B111" s="31"/>
       <c r="C111" s="31"/>
       <c r="D111" s="31"/>
@@ -4763,9 +4599,7 @@
       <c r="Z111" s="17"/>
     </row>
     <row r="112" ht="14.25">
-      <c r="A112" s="22">
-        <v>108</v>
-      </c>
+      <c r="A112" s="22"/>
       <c r="B112" s="31"/>
       <c r="C112" s="31"/>
       <c r="D112" s="31"/>
@@ -4793,9 +4627,7 @@
       <c r="Z112" s="17"/>
     </row>
     <row r="113" ht="14.25">
-      <c r="A113" s="22">
-        <v>109</v>
-      </c>
+      <c r="A113" s="22"/>
       <c r="B113" s="31"/>
       <c r="C113" s="31"/>
       <c r="D113" s="31"/>
@@ -4823,9 +4655,7 @@
       <c r="Z113" s="17"/>
     </row>
     <row r="114" ht="14.25">
-      <c r="A114" s="22">
-        <v>110</v>
-      </c>
+      <c r="A114" s="22"/>
       <c r="B114" s="31"/>
       <c r="C114" s="31"/>
       <c r="D114" s="31"/>
@@ -4853,9 +4683,7 @@
       <c r="Z114" s="17"/>
     </row>
     <row r="115" ht="14.25">
-      <c r="A115" s="22">
-        <v>111</v>
-      </c>
+      <c r="A115" s="22"/>
       <c r="B115" s="31"/>
       <c r="C115" s="31"/>
       <c r="D115" s="31"/>
@@ -4883,9 +4711,7 @@
       <c r="Z115" s="17"/>
     </row>
     <row r="116" ht="14.25">
-      <c r="A116" s="22">
-        <v>112</v>
-      </c>
+      <c r="A116" s="22"/>
       <c r="B116" s="31"/>
       <c r="C116" s="31"/>
       <c r="D116" s="31"/>
@@ -4913,9 +4739,7 @@
       <c r="Z116" s="17"/>
     </row>
     <row r="117" ht="14.25">
-      <c r="A117" s="22">
-        <v>113</v>
-      </c>
+      <c r="A117" s="22"/>
       <c r="B117" s="31"/>
       <c r="C117" s="31"/>
       <c r="D117" s="31"/>
@@ -4943,9 +4767,7 @@
       <c r="Z117" s="17"/>
     </row>
     <row r="118" ht="14.25">
-      <c r="A118" s="22">
-        <v>114</v>
-      </c>
+      <c r="A118" s="22"/>
       <c r="B118" s="31"/>
       <c r="C118" s="31"/>
       <c r="D118" s="31"/>
@@ -4973,9 +4795,7 @@
       <c r="Z118" s="17"/>
     </row>
     <row r="119" ht="14.25">
-      <c r="A119" s="22">
-        <v>115</v>
-      </c>
+      <c r="A119" s="22"/>
       <c r="B119" s="31"/>
       <c r="C119" s="31"/>
       <c r="D119" s="31"/>
@@ -5003,9 +4823,7 @@
       <c r="Z119" s="17"/>
     </row>
     <row r="120" ht="14.25">
-      <c r="A120" s="22">
-        <v>116</v>
-      </c>
+      <c r="A120" s="22"/>
       <c r="B120" s="31"/>
       <c r="C120" s="31"/>
       <c r="D120" s="31"/>
@@ -5033,9 +4851,7 @@
       <c r="Z120" s="17"/>
     </row>
     <row r="121" ht="14.25">
-      <c r="A121" s="22">
-        <v>117</v>
-      </c>
+      <c r="A121" s="22"/>
       <c r="B121" s="31"/>
       <c r="C121" s="31"/>
       <c r="D121" s="31"/>
@@ -5063,9 +4879,7 @@
       <c r="Z121" s="17"/>
     </row>
     <row r="122" ht="14.25">
-      <c r="A122" s="22">
-        <v>118</v>
-      </c>
+      <c r="A122" s="22"/>
       <c r="B122" s="31"/>
       <c r="C122" s="31"/>
       <c r="D122" s="31"/>
@@ -5093,9 +4907,7 @@
       <c r="Z122" s="17"/>
     </row>
     <row r="123" ht="14.25">
-      <c r="A123" s="22">
-        <v>119</v>
-      </c>
+      <c r="A123" s="22"/>
       <c r="B123" s="31"/>
       <c r="C123" s="31"/>
       <c r="D123" s="31"/>
@@ -5123,9 +4935,7 @@
       <c r="Z123" s="17"/>
     </row>
     <row r="124" ht="14.25">
-      <c r="A124" s="22">
-        <v>120</v>
-      </c>
+      <c r="A124" s="22"/>
       <c r="B124" s="31"/>
       <c r="C124" s="31"/>
       <c r="D124" s="31"/>
@@ -5153,9 +4963,7 @@
       <c r="Z124" s="17"/>
     </row>
     <row r="125" ht="14.25">
-      <c r="A125" s="22">
-        <v>121</v>
-      </c>
+      <c r="A125" s="22"/>
       <c r="B125" s="31"/>
       <c r="C125" s="31"/>
       <c r="D125" s="31"/>
@@ -5183,9 +4991,7 @@
       <c r="Z125" s="17"/>
     </row>
     <row r="126" ht="14.25">
-      <c r="A126" s="22">
-        <v>122</v>
-      </c>
+      <c r="A126" s="22"/>
       <c r="B126" s="31"/>
       <c r="C126" s="31"/>
       <c r="D126" s="31"/>
@@ -5213,9 +5019,7 @@
       <c r="Z126" s="17"/>
     </row>
     <row r="127" ht="14.25">
-      <c r="A127" s="22">
-        <v>123</v>
-      </c>
+      <c r="A127" s="22"/>
       <c r="B127" s="31"/>
       <c r="C127" s="31"/>
       <c r="D127" s="31"/>
@@ -5243,9 +5047,7 @@
       <c r="Z127" s="17"/>
     </row>
     <row r="128" ht="14.25">
-      <c r="A128" s="22">
-        <v>124</v>
-      </c>
+      <c r="A128" s="22"/>
       <c r="B128" s="31"/>
       <c r="C128" s="31"/>
       <c r="D128" s="31"/>
@@ -5273,9 +5075,7 @@
       <c r="Z128" s="17"/>
     </row>
     <row r="129" ht="14.25">
-      <c r="A129" s="22">
-        <v>125</v>
-      </c>
+      <c r="A129" s="22"/>
       <c r="B129" s="31"/>
       <c r="C129" s="31"/>
       <c r="D129" s="31"/>
@@ -5303,9 +5103,7 @@
       <c r="Z129" s="17"/>
     </row>
     <row r="130" ht="14.25">
-      <c r="A130" s="22">
-        <v>126</v>
-      </c>
+      <c r="A130" s="22"/>
       <c r="B130" s="31"/>
       <c r="C130" s="31"/>
       <c r="D130" s="31"/>
@@ -5333,9 +5131,7 @@
       <c r="Z130" s="17"/>
     </row>
     <row r="131" ht="14.25">
-      <c r="A131" s="22">
-        <v>127</v>
-      </c>
+      <c r="A131" s="22"/>
       <c r="B131" s="31"/>
       <c r="C131" s="31"/>
       <c r="D131" s="31"/>
@@ -5363,9 +5159,7 @@
       <c r="Z131" s="17"/>
     </row>
     <row r="132" ht="14.25">
-      <c r="A132" s="22">
-        <v>128</v>
-      </c>
+      <c r="A132" s="22"/>
       <c r="B132" s="31"/>
       <c r="C132" s="31"/>
       <c r="D132" s="31"/>
@@ -5393,9 +5187,7 @@
       <c r="Z132" s="17"/>
     </row>
     <row r="133" ht="14.25">
-      <c r="A133" s="22">
-        <v>129</v>
-      </c>
+      <c r="A133" s="22"/>
       <c r="B133" s="31"/>
       <c r="C133" s="31"/>
       <c r="D133" s="31"/>
@@ -5423,9 +5215,7 @@
       <c r="Z133" s="17"/>
     </row>
     <row r="134" ht="14.25">
-      <c r="A134" s="22">
-        <v>130</v>
-      </c>
+      <c r="A134" s="22"/>
       <c r="B134" s="31"/>
       <c r="C134" s="31"/>
       <c r="D134" s="31"/>
@@ -5453,9 +5243,7 @@
       <c r="Z134" s="17"/>
     </row>
     <row r="135" ht="14.25">
-      <c r="A135" s="22">
-        <v>131</v>
-      </c>
+      <c r="A135" s="22"/>
       <c r="B135" s="31"/>
       <c r="C135" s="31"/>
       <c r="D135" s="31"/>
@@ -5483,9 +5271,7 @@
       <c r="Z135" s="17"/>
     </row>
     <row r="136" ht="14.25">
-      <c r="A136" s="22">
-        <v>132</v>
-      </c>
+      <c r="A136" s="22"/>
       <c r="B136" s="31"/>
       <c r="C136" s="31"/>
       <c r="D136" s="31"/>
@@ -5513,9 +5299,7 @@
       <c r="Z136" s="17"/>
     </row>
     <row r="137" ht="14.25">
-      <c r="A137" s="22">
-        <v>133</v>
-      </c>
+      <c r="A137" s="22"/>
       <c r="B137" s="31"/>
       <c r="C137" s="31"/>
       <c r="D137" s="31"/>
@@ -5543,9 +5327,7 @@
       <c r="Z137" s="17"/>
     </row>
     <row r="138" ht="14.25">
-      <c r="A138" s="22">
-        <v>134</v>
-      </c>
+      <c r="A138" s="22"/>
       <c r="B138" s="31"/>
       <c r="C138" s="31"/>
       <c r="D138" s="31"/>
@@ -5573,9 +5355,7 @@
       <c r="Z138" s="17"/>
     </row>
     <row r="139" ht="14.25">
-      <c r="A139" s="22">
-        <v>135</v>
-      </c>
+      <c r="A139" s="22"/>
       <c r="B139" s="31"/>
       <c r="C139" s="31"/>
       <c r="D139" s="31"/>
@@ -5603,9 +5383,7 @@
       <c r="Z139" s="17"/>
     </row>
     <row r="140" ht="14.25">
-      <c r="A140" s="22">
-        <v>136</v>
-      </c>
+      <c r="A140" s="22"/>
       <c r="B140" s="31"/>
       <c r="C140" s="31"/>
       <c r="D140" s="31"/>
@@ -5633,9 +5411,7 @@
       <c r="Z140" s="17"/>
     </row>
     <row r="141" ht="14.25">
-      <c r="A141" s="22">
-        <v>137</v>
-      </c>
+      <c r="A141" s="22"/>
       <c r="B141" s="31"/>
       <c r="C141" s="31"/>
       <c r="D141" s="31"/>
@@ -5663,9 +5439,7 @@
       <c r="Z141" s="17"/>
     </row>
     <row r="142" ht="14.25">
-      <c r="A142" s="22">
-        <v>138</v>
-      </c>
+      <c r="A142" s="22"/>
       <c r="B142" s="31"/>
       <c r="C142" s="31"/>
       <c r="D142" s="31"/>
@@ -5693,9 +5467,7 @@
       <c r="Z142" s="17"/>
     </row>
     <row r="143" ht="14.25">
-      <c r="A143" s="22">
-        <v>139</v>
-      </c>
+      <c r="A143" s="22"/>
       <c r="B143" s="31"/>
       <c r="C143" s="31"/>
       <c r="D143" s="31"/>
@@ -5723,9 +5495,7 @@
       <c r="Z143" s="17"/>
     </row>
     <row r="144" ht="14.25">
-      <c r="A144" s="22">
-        <v>140</v>
-      </c>
+      <c r="A144" s="22"/>
       <c r="B144" s="31"/>
       <c r="C144" s="31"/>
       <c r="D144" s="31"/>
@@ -5753,9 +5523,7 @@
       <c r="Z144" s="17"/>
     </row>
     <row r="145" ht="14.25">
-      <c r="A145" s="22">
-        <v>141</v>
-      </c>
+      <c r="A145" s="22"/>
       <c r="B145" s="31"/>
       <c r="C145" s="31"/>
       <c r="D145" s="31"/>
@@ -29772,113 +29540,8 @@
     <mergeCell ref="P3:R3"/>
     <mergeCell ref="S3:V3"/>
   </mergeCells>
-  <dataValidations count="42" disablePrompts="0">
-    <dataValidation sqref="B5:B6 B8 B10:B11 B13 B15:B17 B19 B21 B23 B25 B27 B29:B1001" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="J5:J8 J10:J11 J13 J15:J17 J19 J21 J23 J25 J27 J29:J100" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="E5:E6 E8 E10:E11 E13 E15:E17 E19 E21 E23 E25 E27 E29:E1001" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="B7" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E7" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F1:F8 F10:F11 F13 F15:F17 F19 F21 F23 F25 F27 F29:F1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J9" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B9" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E9" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F9" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J12" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B12" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E12" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F12" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J14" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B14" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E14" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F14" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J18" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B18" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E18" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F18" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J20" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B20" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E20" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F20" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E22" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F22" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J24" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E24" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F24" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J26" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B26" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E26" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F26" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
-    <dataValidation sqref="J28" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$C$2:$C$81</formula1>
-    </dataValidation>
-    <dataValidation sqref="B28" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="E28" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$K$2:$K$5</formula1>
-    </dataValidation>
-    <dataValidation sqref="F28" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" promptTitle="" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
